--- a/event_planner_forms/007_st_patrick_s_day_celebration_feedback_survey--event_planner_forms.xlsx
+++ b/event_planner_forms/007_st_patrick_s_day_celebration_feedback_survey--event_planner_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1245,17 +1245,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>event_planner_forms_7_choices</t>
+          <t>event_planner_forms_8_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>shepherd's_pie</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Shepherd's Pie</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1284,29 +1284,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>event_planner_forms_8_choices</t>
+          <t>event_planner_forms_9_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>somewhat</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Somewhat</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1335,29 +1335,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>event_planner_forms_9_choices</t>
+          <t>event_planner_forms_10_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>somewhat</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Somewhat</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1386,29 +1386,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>event_planner_forms_10_choices</t>
+          <t>event_planner_forms_15_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>somewhat</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Somewhat</t>
+          <t>Very Likely</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>very_likely</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Very Likely</t>
+          <t>Somewhat Likely</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>somewhat_likely</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Somewhat Likely</t>
+          <t>Not Likely</t>
         </is>
       </c>
     </row>
@@ -1454,29 +1454,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_likely</t>
+          <t>not_at_all_likely</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Not Likely</t>
+          <t>Not at All Likely</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>event_planner_forms_15_choices</t>
+          <t>event_planner_forms_16_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>not_at_all_likely</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Not at All Likely</t>
+          <t>Very Likely</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>very_likely</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Very Likely</t>
+          <t>Somewhat Likely</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>somewhat_likely</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Somewhat Likely</t>
+          <t>Not Likely</t>
         </is>
       </c>
     </row>
@@ -1522,27 +1522,10 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>not_likely</t>
+          <t>not_at_all_likely</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
-        <is>
-          <t>Not Likely</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>event_planner_forms_16_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>not_at_all_likely</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
         <is>
           <t>Not at All Likely</t>
         </is>
